--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_05_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_05_19_Cau.xlsx
@@ -675,7 +675,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ phạm vi đối tượng và nhiệm vụ trong kết luận trùng với phạm vi của bài đánh giá.</t>
+          <t>Đạt 99% trên một bài đánh giá an toàn cố định chỉ chứng minh mô hình có hiệu năng cao trên phân phối của bài đánh giá đó; trong thực tế triển khai, mô hình vẫn cần được kiểm thử trên các phân phối và kiểu tấn công đối kháng khác.</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn bằng chứng quan sát hành vi trong nhiều điều kiện; đừng coi tên thuật toán là bảo chứng.</t>
+          <t>Đánh giá an toàn toàn diện cần: Red-team bằng lời nhắc đối kháng (a), Đánh giá trên phân phối thực tế (b), Theo dõi dạng lỗi và độ không chắc chắn (c), và Kiểm tra mức tuân thủ chính sách theo rubric (e). Chỉ biết tên phương pháp (d) không phải là bằng chứng kiểm chứng.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi thay đổi xảy ra trước mô hình nền, sau mô hình nền hay trong lúc suy luận.</t>
+          <t>Tăng kho dữ liệu và năng lực tính toán cho việc dự đoán token kế tiếp (x1) thuộc Tiền huấn luyện pre-training (r1); Tinh chỉnh theo chỉ dẫn/ưu tiên sau khi có base model (x2) thuộc Hậu huấn luyện post-training (r2); Giữ nguyên trọng số, thực hiện thêm nhiều bước suy luận/tìm kiếm khi trả lời (x3) thuộc Tính toán tại thời điểm suy luận test-time compute (r3).</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
@@ -847,7 +851,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính token đầu vào và đầu ra riêng theo đúng đơn giá, rồi mới cộng hai khoản.</t>
+          <t>Chi phí token đầu vào = 120.000 × (2 USD / 1.000.000) = 0,24 USD. Chi phí token đầu ra = 30.000 × (8 USD / 1.000.000) = 0,24 USD. Tổng chi phí là 0,24 + 0,24 = 0,48 USD.</t>
         </is>
       </c>
     </row>
@@ -867,7 +871,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
@@ -881,7 +889,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính tổng chi phí của từng nhà cung cấp bằng hai đơn giá riêng, rồi lấy chi phí của B trừ chi phí của A.</t>
+          <t>Chi phí tại Nhà cung cấp A = (800.000 × 0,50 + 200.000 × 1,50) / 1.000.000 = 0,40 + 0,30 = 0,70 USD. Chi phí tại Nhà cung cấp B = (800.000 × 0,70 + 200.000 × 1,00) / 1.000.000 = 0,56 + 0,20 = 0,76 USD. Chênh lệch chi phí: B − A = 0,76 − 0,70 = 0,06 USD (A rẻ hơn B 0,06 USD).</t>
         </is>
       </c>
     </row>
@@ -902,7 +910,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -916,7 +928,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số token của một request với 50 trước, rồi áp riêng hai đơn giá.</t>
+          <t>Tổng số token đầu vào cả lô = 50 × 4.000 = 200.000 token, chi phí đầu vào = 200.000 × (3 / 1.000.000) = 0,60 USD. Tổng số token đầu ra cả lô = 50 × 1.000 = 50.000 token, chi phí đầu ra = 50.000 × (9 / 1.000.000) = 0,45 USD. Tổng chi phí toàn bộ lô = 0,60 + 0,45 = 1,05 USD.</t>
         </is>
       </c>
     </row>
@@ -936,7 +948,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -950,7 +966,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hạch toán từng request riêng; phần lịch sử được gửi lại vẫn được tính trong request mới.</t>
+          <t>Tổng số token đầu vào qua ba lượt = 1.000 + 1.800 + 2.600 = 5.400 token. Tổng số token đầu ra qua ba lượt = 3 × 400 = 1.200 token. Tổng số token được hạch toán là 5.400 + 1.200 = 6.600 token.</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1052,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giảm phần lặp không liên quan, nhưng không được xóa mù quáng dữ kiện bắt buộc.</t>
+          <t>Các biện pháp giảm chi phí token lặp lại hợp lý: Tóm tắt có kiểm soát lịch sử cũ (a), Chỉ truy xuất đoạn tài liệu liên quan cho từng request (b), và Giới hạn số lượt lịch sử giữ nguyên văn (d). Giữ nguyên toàn bộ nhật ký (c) không giảm chi phí, còn lược bỏ chỉ dẫn bắt buộc (e) làm hỏng chất lượng.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1106,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Loại hồ sơ vi phạm giới hạn bắt buộc về ngữ cảnh trước khi so sánh chi phí và chất lượng.</t>
+          <t>Hợp đồng có 90k token đầu vào và 8k token đầu ra (tổng 98k token), vượt giới hạn 32k của Tier S, trong khi Tier L quá đắt vượt ngân sách hạn chế. Do đó Tier M với ngữ cảnh 128k và chi phí vừa phải là lựa chọn phù hợp nhất.</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1217,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ mọi yếu tố ngoài danh tính model càng nhất quán càng tốt.</t>
+          <t>Trong thí nghiệm so sánh hai mô hình, mọi yếu tố ngoài danh tính mô hình (e) đều là biến gây nhiễu cần chuẩn hóa: Prompt và ngôn ngữ khác nhau (a), Temperature khác nhau (b), Chỉ chạy 1 lần không đo được phương sai (c), và Ranh giới đo độ trễ khác nhau (d).</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1306,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ đủ dữ liệu để người khác tái lập lý do một model được chọn.</t>
+          <t>Để tái lập và kiểm tra lại phép so sánh model, schema kết quả cần ghi nhận: ID mô hình và case_id/prompt (a), Các tham số sinh như temperature, top_p (b), Đầu ra thô và điểm số theo rubric (c), cùng Độ trễ và số token sử dụng (d).</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1356,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi ai gọi model, qua giao diện nào và ai chịu trách nhiệm về hạ tầng.</t>
+          <t>Cá nhân hỏi đáp thủ công, không cần tích hợp (x1) dùng Giao diện trò chuyện Chat UI (r1); IDE cần gợi ý code theo repository (x2) dùng Trợ lý lập trình coding assistant (r2); Phần backend gọi model theo từng request (x3) dùng API do nhà cung cấp vận hành hosted API (r3); Tổ chức giữ trọng số và suy luận trong hạ tầng riêng (x4) dùng Tự vận hành self-hosted (r4).</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1438,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn giao diện đáp ứng trường hợp sử dụng hiện tại, không tối ưu cho nhu cầu chưa có.</t>
+          <t>Khi chỉ cần thử nghiệm ý tưởng trong 30 phút bằng vài prompt thủ công mà chưa cần viết code hay tích hợp, Giao diện trò chuyện (Chat UI) là chế độ có chi phí chuẩn bị thấp nhất và nhanh nhất.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_05_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_05_19_Cau.xlsx
@@ -624,10 +624,17 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt việc giảm tần suất lỗi trong một bài đánh giá với việc lỗi không thể xảy ra.
-Phân tích theo nguyên lý thiết kế: Phân biệt việc giảm tần suất lỗi trong một bài đánh giá với việc lỗi không thể xảy ra.</t>
+- Đánh giá phần được hỗ trợ (1.0 điểm): Thừa nhận RLHF giúp giảm thiểu tần suất vi phạm an toàn trong điều kiện thông thường.
+- Phân tích vì sao kết luận tuyệt đối không hợp lệ (2.0 điểm): Chỉ ra bản chất mô hình xác suất và nguy cơ bị jailbreak/prompt injection phá vỡ lớp vỏ an toàn bề mặt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Phần có thể được hỗ trợ: Nhận định đúng ở chỗ RLHF (Reinforcement Learning from Human Feedback) làm giảm đáng kể xác suất và tần suất sinh ra các nội dung độc hại, thiên kiến, hoặc nguy hiểm trong các bài kiểm thử tiêu chuẩn và tương tác hội thoại thông thường thông qua việc học phạt các phản hồi vi phạm.
+- Vì sao kết luận tuyệt đối ('không thể tạo ra đầu ra nguy hiểm') là KHÔNG HỢP LỆ:
+1. Bản chất mô hình xác suất: LLM là mô hình xác suất sinh (probabilistic generative model), không gian đầu vào mở vô hạn nên luôn tồn tại xác suất khác không sinh ra nội dung nguy hại.
+2. Điểm yếu trước tấn công đối kháng: RLHF chỉ căn chỉnh bề mặt phân phối (surface-level alignment). Mô hình vẫn dễ dàng bị bẻ khóa (jailbreak) thông qua prompt injection, kỹ thuật nhập vai đối kháng (adversarial roleplay, DAN), hoặc mã hóa đối kháng (Base64, đa ngôn ngữ ít phổ biến), khiến cơ chế phòng thủ bị vô hiệu hóa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Định lý an toàn AI chỉ ra rằng việc căn chỉnh trọng số (post-training alignment) chỉ làm giảm rủi ro chứ không thể mang lại sự đảm bảo an toàn tuyệt đối mang tính hình thức (formal verification). Một hệ thống AI production bắt buộc phải triển khai mô hình phòng thủ theo chiều sâu (Defense-in-Depth) với các bộ lọc Input/Output Guardrails độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Wei, A., et al. (2024). Jailbroken: How Does LLM Safety Training Fail? NeurIPS 2023. https://arxiv.org/abs/2307.02483; OWASP Top 10 for Large Language Model Applications - LLM01: Prompt Injection.</t>
         </is>
       </c>
     </row>
@@ -810,10 +817,15 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra xem bộ tối ưu (optimizer) có cập nhật trọng số trước triển khai hay hệ thống chỉ làm thêm việc cho từng truy vấn.
-Phân tích theo nguyên lý thiết kế: Kiểm tra xem bộ tối ưu (optimizer) có cập nhật trọng số trước triển khai hay hệ thống chỉ làm thêm việc cho từng truy vấn.</t>
+- Phân loại đúng trục cải tiến (1.5 điểm): Xác định chính xác Inference-time compute (Test-time compute scaling / Best-of-N sampling).
+- Chỉ ra bằng chứng quyết định (1.5 điểm): Nêu rõ checkpoint mô hình được giữ nguyên và tài nguyên tính toán bổ sung hoàn toàn diễn ra tại runtime trên từng truy vấn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Phân loại trục cải tiến: Trục cải tiến tính toán tại thời điểm suy luận (Inference-Time Compute Scaling / Test-Time Compute / Best-of-N Sampling).
+- Bằng chứng quyết định: Hệ thống giữ nguyên hoàn toàn checkpoint và trọng số của mô hình (không hề có quá trình cập nhật gradient, fine-tuning hay huấn luyện thêm trước khi triển khai). Toàn bộ chi phí tính toán tăng thêm được dồn vào runtime cho từng truy vấn cụ thể: sinh song song 8 phương án ứng viên và dùng bộ kiểm chứng (Verifier/Reward Model) để chọn ra phương án có độ tin cậy cao nhất.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mở rộng khả năng của hệ thống AI hiện nay có hai trục: Trục huấn luyện (Pretraining / Post-training compute) và Trục suy luận (Inference-time compute scaling). Việc tăng tính toán suy luận (System 2 thinking / Re-ranking / Verification) cho phép đạt độ chính xác vượt bậc trên các bài toán lập luận logic phức tạp mà không cần tái huấn luyện mô hình nền tảng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Brown, B., et al. (2024). Large Language Monkeys: Scaling Inference Compute with Repeated Sampling. arXiv:2407.21787. https://arxiv.org/abs/2407.21787; Snell, C., et al. (2024). Scaling LLM Test-Time Compute Optimally.</t>
         </is>
       </c>
     </row>
@@ -997,10 +1009,15 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết 2.000 token cho mỗi request rồi cộng đủ 100 request.
-Phân tích theo nguyên lý thiết kế: Viết 2.000 token cho mỗi request rồi cộng đủ 100 request.</t>
+- Tính đúng số token hạch toán (1.5 điểm): Tính chính xác 200.000 token đầu vào (2.000 × 100).
+- Giải thích bản chất hạch toán (1.5 điểm): Giải thích rõ API là stateless, mỗi request phải nạp và xử lý prefill lại toàn bộ system prompt từ đầu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Số token đầu vào được hạch toán: 2.000 token × 100 request = 200.000 token đầu vào.
+- Vì sao không phải chỉ 2.000 token: Các giao thức API LLM thương mại hoạt động theo nguyên lý phi trạng thái (stateless HTTP requests). Mỗi request là một phiên xử lý độc lập hoàn toàn; server LLM phải đọc và chạy qua giai đoạn prefill (tính toán biểu diễn ma trận KV cache) cho toàn bộ 2.000 token của system prompt trong từng request đó. Do đó, nhà cung cấp dịch vụ hạch toán chi phí đầu vào tích lũy tuyến tính cho mỗi lượt gọi: 2.000 × 100 = 200.000 token (trừ khi có tính năng Prompt Caching được áp dụng với biểu giá chiết khấu riêng).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Bản chất phi trạng thái của HTTP API buộc các hệ thống phân tán phải trả chi phí tính toán lặp lại trên các tiền tố prompt tĩnh dài. Trong kiến trúc hiện đại, giải pháp tối ưu chi phí là kích hoạt Prompt Caching (Prefix Caching) tại gateway để tái sử dụng KV cache giữa các request có cùng tiền tố.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI API Pricing &amp; Token Billing Model (https://openai.com/api/pricing/); Anthropic Claude Documentation - Prompt Caching Architecture.</t>
         </is>
       </c>
     </row>
@@ -1251,10 +1268,23 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nhóm biến kiểm soát theo dữ liệu đầu vào, thiết lập sinh, số lần lặp và cách đo.
-Phân tích theo nguyên lý thiết kế: Nhóm biến kiểm soát theo dữ liệu đầu vào, thiết lập sinh, số lần lặp và cách đo.</t>
+- Sửa đổi quy trình thử nghiệm chuẩn hóa (2.0 điểm): Chuẩn hóa cùng tập prompt, cùng tham số temperature/sinh, chạy lặp lại nhiều lần và đồng nhất mốc đo độ trễ.
+- Nêu đủ 4 biến kiểm soát/trường thông tin (2.0 điểm): Liệt kê đủ 4 trường thiết yếu (prompt hash/text, tham số sinh, chỉ số latency chuẩn, token usage).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa đổi quy trình thử nghiệm tối thiểu có thể so sánh:
+- Chuẩn hóa tập prompt đầu vào: Sử dụng cùng một tập dữ liệu benchmark cố định, cùng nội dung và cùng một ngôn ngữ cho cả hai mô hình (loại bỏ prompt khác ngôn ngữ).
+- Đồng nhất tham số sinh: Cố định cùng một giá trị `temperature` (thường là 0.0 để đảm bảo tính tất định), cùng `top_p` và `max_tokens`.
+- Tăng số lần thử nghiệm lặp lại: Chạy lặp lại nhiều lần (ví dụ N = 10 đến 30 lượt trên mỗi prompt) để tính toán các giá trị thống kê (trung vị, trung bình, P95) thay vì chỉ chạy 1 lần duy nhất.
+- Đồng nhất ranh giới đo lường thời gian: Đo round-trip time thuần túy từ thời điểm gửi HTTP request đến khi nhận token cuối cùng, loại bỏ chi phí khởi tạo client ban đầu.
+2. Bốn biến kiểm soát hoặc trường thông tin cần lưu trữ trong nhật ký đánh giá:
+1) `prompt_hash`: Định danh duy nhất và nội dung chuẩn hóa của prompt đầu vào.
+2) `generation_params`: Bản ghi các tham số sinh (`temperature`, `top_p`, `seed`, `max_tokens`).
+3) `latency_breakdown`: Thời gian phản hồi phân rã (`time_to_first_token_ms`, `total_duration_ms`).
+4) `token_usage`: Số lượng token đầu vào và đầu ra thực tế (`prompt_tokens`, `completion_tokens`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thiết kế thí nghiệm so sánh đối chứng (A/B Testing / Benchmarking) đòi hỏi kiểm soát nghiêm ngặt nguyên tắc đơn biến (Single Variable Principle). Bất kỳ sự khác biệt nào về ngôn ngữ prompt, tham số ngẫu nhiên hay ranh giới đo lường đều tạo ra các biến gây nhiễu (confounding variables), làm vô hiệu hóa giá trị khoa học của kết quả so sánh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Liang, P., et al. (2022). Holistic Evaluation of Language Models (HELM). Stanford CRFM. https://arxiv.org/abs/2211.09110; MLPerf Inference Benchmark Suite.</t>
         </is>
       </c>
     </row>
@@ -1387,10 +1417,17 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chọn chế độ thỏa điều kiện dữ liệu trước, rồi nêu chi phí vận hành đi kèm.
-Phân tích theo nguyên lý thiết kế: Chọn chế độ thỏa điều kiện dữ liệu trước, rồi nêu chi phí vận hành đi kèm.</t>
+- Chọn đúng chế độ truy cập (1.5 điểm): Xác định đúng giải pháp On-premises / Self-hosted mã nguồn mở trên cụm máy chủ bệnh viện.
+- Nêu rõ các đánh đổi kỹ thuật và chi phí (1.5 điểm): Phân tích chi phí phần cứng/vận hành hạ tầng cao và nỗ lực tối ưu năng lực mô hình so với cloud API.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Chế độ truy cập ưu tiên: Tự triển khai mô hình mã nguồn mở cục bộ trên hạ tầng nội bộ (On-premises / Self-hosted Open-Weight Models, chẳng hạn như Llama 3, Qwen 2.5 hoặc Mistral triển khai qua vLLM/TGI trên cụm máy chủ GPU của bệnh viện).
+- Đánh đổi chính (Trade-offs):
+1. Chi phí đầu tư và vận hành cao: Đòi hỏi chi phí vốn lớn (CapEx) cho phần cứng GPU chuyên dụng, điện năng, làm mát và đội ngũ kỹ sư chuyên trách để duy trì độ sẵn sàng, sao lưu và tối ưu throughput.
+2. Khoảng cách về năng lực mô hình: Các mô hình open-weights chạy cục bộ có thể đòi hỏi nhiều công sức fine-tuning chuyên ngành y khoa để đạt được độ chính xác tương đương với các mô hình thương mại đóng hàng đầu trên đám mây.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong lĩnh vực y tế (Healthcare), tính bảo mật dữ liệu bệnh nhân (tuân thủ tiêu chuẩn HIPAA, GDPR) và khả năng kiểm toán quá trình suy luận (auditability) là các ràng buộc cứng (Hard Constraints). Khi tổ chức có sẵn đội ngũ vận hành GPU, kiến trúc On-premises là lựa chọn tối ưu để loại bỏ hoàn toàn rủi ro rò rỉ dữ liệu qua mạng bên thứ ba.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+HIPAA Security Rule &amp; AI Deployment Guidance (https://www.hhs.gov/hipaa/); NIST AI Risk Management Framework (NIST AI 100-1).</t>
         </is>
       </c>
     </row>
